--- a/docs/Restful-booker_API_테스트케이스.xlsx
+++ b/docs/Restful-booker_API_테스트케이스.xlsx
@@ -356,7 +356,7 @@
     <t xml:space="preserve">문서 버전</t>
   </si>
   <si>
-    <t xml:space="preserve">v1.1</t>
+    <t xml:space="preserve">v1.2</t>
   </si>
   <si>
     <t xml:space="preserve">테스트 실행일</t>
@@ -2474,7 +2474,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(admin / password123)
+      <t xml:space="preserve">({{username}} / {{password}})
 2. POST /booking</t>
     </r>
     <r>
@@ -2720,7 +2720,33 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">수정 후 재조회</t>
+      <t xml:space="preserve">수정 후 재조회 → 예약 삭제 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">정리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
     </r>
   </si>
   <si>
@@ -2981,7 +3007,68 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">실제 로그</t>
+      <t xml:space="preserve">실제 로그
+예약 삭제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">상태 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">200·201·204 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">판정 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">테스트 데이터 정리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
     </r>
   </si>
   <si>

--- a/docs/Restful-booker_API_테스트케이스.xlsx
+++ b/docs/Restful-booker_API_테스트케이스.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="453">
   <si>
     <r>
       <rPr>
@@ -356,7 +356,7 @@
     <t xml:space="preserve">문서 버전</t>
   </si>
   <si>
-    <t xml:space="preserve">v1.2</t>
+    <t xml:space="preserve">v1.3</t>
   </si>
   <si>
     <t xml:space="preserve">테스트 실행일</t>
@@ -368,7 +368,7 @@
     <t xml:space="preserve">최종 업데이트</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-28</t>
+    <t xml:space="preserve">2026-10-31</t>
   </si>
   <si>
     <r>
@@ -2201,7 +2201,33 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Status</t>
+      <t xml:space="preserve">Status
+200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이면 응답이 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">schema.bookingCreated</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">와 일치</t>
     </r>
   </si>
   <si>
@@ -2394,7 +2420,42 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">와 응답 전체를 로그로 기록</t>
+      <t xml:space="preserve">와 응답 전체를 로그로 기록
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이면 응답 스키마</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(schema.bookingCreated) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">검증</t>
     </r>
   </si>
   <si>
@@ -2542,6 +2603,68 @@
 Accept: application/json</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">상태 코드 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">== </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">데이터셋의 기대 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Status
+200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이면 응답이 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">schema.booking</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">과 일치</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">GET {{baseUrl}}/booking/{{bookingid}}</t>
   </si>
   <si>
@@ -2815,10 +2938,54 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">예약생성</t>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Auth: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">토큰 발급 판정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">응답 스키마</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(schema.auth) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">검증
+예약생성</t>
     </r>
     <r>
       <rPr>
@@ -2853,6 +3020,40 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">판정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">응답 스키마</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(schema.bookingCreated) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">검증</t>
     </r>
     <r>
       <rPr>
@@ -2921,7 +3122,41 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">판정
+      <t xml:space="preserve">판정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, 200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이면 응답 스키마</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(schema.booking) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">검증
 재조회</t>
     </r>
     <r>
@@ -3007,7 +3242,41 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">실제 로그
+      <t xml:space="preserve">실제 로그</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">응답 스키마</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(schema.booking) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">검증
 예약 삭제</t>
     </r>
     <r>
@@ -10759,35 +11028,35 @@
         <v>99</v>
       </c>
       <c r="I3" s="28" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="J3" s="29" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K3" s="28" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L3" s="29" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M3" s="28" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N3" s="27" t="n">
         <f aca="false">COUNTA(부분수정_데이터!$A$2:$A$200)</f>
         <v>33</v>
       </c>
       <c r="O3" s="29" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P3" s="28" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q3" s="28" t="s">
         <v>122</v>
       </c>
+      <c r="Q3" s="29" t="s">
+        <v>123</v>
+      </c>
       <c r="R3" s="29" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -10834,43 +11103,43 @@
         <v>24</v>
       </c>
       <c r="C1" s="22" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D1" s="22" t="s">
         <v>76</v>
       </c>
       <c r="E1" s="22" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F1" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G1" s="24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H1" s="24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I1" s="24" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J1" s="24" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K1" s="32" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L1" s="32" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M1" s="32" t="s">
         <v>67</v>
       </c>
       <c r="N1" s="32" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O1" s="32" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P1" s="22" t="s">
         <v>71</v>
@@ -10878,31 +11147,31 @@
     </row>
     <row r="2" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="29" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B2" s="27" t="s">
         <v>92</v>
       </c>
       <c r="C2" s="28" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D2" s="28" t="s">
+        <v>137</v>
+      </c>
+      <c r="E2" s="28" t="s">
         <v>136</v>
       </c>
-      <c r="E2" s="28" t="s">
-        <v>135</v>
-      </c>
       <c r="F2" s="28" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G2" s="30" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H2" s="27" t="n">
         <v>200</v>
       </c>
       <c r="I2" s="29" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J2" s="29" t="s">
         <v>102</v>
@@ -10911,7 +11180,7 @@
         <v>200</v>
       </c>
       <c r="L2" s="28" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M2" s="27" t="s">
         <v>26</v>
@@ -10924,31 +11193,31 @@
     </row>
     <row r="3" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="29" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B3" s="27" t="s">
         <v>92</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F3" s="28" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G3" s="30" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H3" s="27" t="n">
         <v>200</v>
       </c>
       <c r="I3" s="29" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J3" s="29" t="s">
         <v>102</v>
@@ -10957,7 +11226,7 @@
         <v>200</v>
       </c>
       <c r="L3" s="28" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M3" s="27" t="s">
         <v>26</v>
@@ -10970,31 +11239,31 @@
     </row>
     <row r="4" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="29" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B4" s="27" t="s">
         <v>92</v>
       </c>
       <c r="C4" s="28" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D4" s="29" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E4" s="28" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F4" s="28" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G4" s="30" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H4" s="27" t="n">
         <v>400</v>
       </c>
       <c r="I4" s="28" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J4" s="29" t="s">
         <v>102</v>
@@ -11003,13 +11272,13 @@
         <v>200</v>
       </c>
       <c r="L4" s="29" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M4" s="27" t="s">
         <v>27</v>
       </c>
       <c r="N4" s="27" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O4" s="28"/>
       <c r="P4" s="27" t="n">
@@ -11018,31 +11287,31 @@
     </row>
     <row r="5" customFormat="false" ht="129.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="29" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B5" s="27" t="s">
         <v>92</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D5" s="29" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E5" s="28" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F5" s="28" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G5" s="30" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H5" s="27" t="n">
         <v>400</v>
       </c>
       <c r="I5" s="28" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J5" s="29" t="s">
         <v>102</v>
@@ -11051,16 +11320,16 @@
         <v>200</v>
       </c>
       <c r="L5" s="29" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M5" s="27" t="s">
         <v>27</v>
       </c>
       <c r="N5" s="27" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O5" s="29" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P5" s="27" t="n">
         <v>4</v>
@@ -11068,31 +11337,31 @@
     </row>
     <row r="6" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="29" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B6" s="27" t="s">
         <v>92</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F6" s="28" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G6" s="30" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H6" s="27" t="n">
         <v>400</v>
       </c>
       <c r="I6" s="28" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J6" s="29" t="s">
         <v>102</v>
@@ -11101,13 +11370,13 @@
         <v>500</v>
       </c>
       <c r="L6" s="28" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M6" s="27" t="s">
         <v>27</v>
       </c>
       <c r="N6" s="27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O6" s="28"/>
       <c r="P6" s="27" t="n">
@@ -11116,31 +11385,31 @@
     </row>
     <row r="7" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="29" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B7" s="27" t="s">
         <v>92</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D7" s="28" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E7" s="28" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F7" s="28" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G7" s="30" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H7" s="27" t="n">
         <v>400</v>
       </c>
       <c r="I7" s="28" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J7" s="29" t="s">
         <v>102</v>
@@ -11149,13 +11418,13 @@
         <v>200</v>
       </c>
       <c r="L7" s="29" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M7" s="27" t="s">
         <v>27</v>
       </c>
       <c r="N7" s="27" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="O7" s="28"/>
       <c r="P7" s="27" t="n">
@@ -11164,31 +11433,31 @@
     </row>
     <row r="8" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="29" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B8" s="27" t="s">
         <v>92</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F8" s="28" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G8" s="30" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H8" s="27" t="n">
         <v>400</v>
       </c>
       <c r="I8" s="28" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J8" s="29" t="s">
         <v>102</v>
@@ -11197,13 +11466,13 @@
         <v>200</v>
       </c>
       <c r="L8" s="29" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M8" s="27" t="s">
         <v>27</v>
       </c>
       <c r="N8" s="27" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O8" s="28"/>
       <c r="P8" s="27" t="n">
@@ -11212,31 +11481,31 @@
     </row>
     <row r="9" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="29" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B9" s="27" t="s">
         <v>92</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E9" s="29" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F9" s="29" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H9" s="27" t="n">
         <v>400</v>
       </c>
       <c r="I9" s="28" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J9" s="29" t="s">
         <v>102</v>
@@ -11245,16 +11514,16 @@
         <v>200</v>
       </c>
       <c r="L9" s="29" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M9" s="27" t="s">
         <v>27</v>
       </c>
       <c r="N9" s="27" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O9" s="28" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P9" s="27" t="n">
         <v>8</v>
@@ -11262,31 +11531,31 @@
     </row>
     <row r="10" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="29" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B10" s="27" t="s">
         <v>92</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D10" s="29" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E10" s="29" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F10" s="29" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G10" s="30" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H10" s="27" t="n">
         <v>400</v>
       </c>
       <c r="I10" s="28" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J10" s="29" t="s">
         <v>102</v>
@@ -11295,16 +11564,16 @@
         <v>200</v>
       </c>
       <c r="L10" s="29" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M10" s="27" t="s">
         <v>27</v>
       </c>
       <c r="N10" s="27" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O10" s="28" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P10" s="27" t="n">
         <v>9</v>
@@ -11370,43 +11639,43 @@
         <v>24</v>
       </c>
       <c r="C1" s="22" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D1" s="22" t="s">
         <v>76</v>
       </c>
       <c r="E1" s="22" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F1" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G1" s="24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H1" s="24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I1" s="24" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J1" s="24" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K1" s="32" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L1" s="32" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M1" s="32" t="s">
         <v>67</v>
       </c>
       <c r="N1" s="32" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O1" s="32" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P1" s="22" t="s">
         <v>71</v>
@@ -11414,40 +11683,40 @@
     </row>
     <row r="2" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="29" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B2" s="27" t="s">
         <v>109</v>
       </c>
       <c r="C2" s="28" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E2" s="29" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F2" s="28" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G2" s="30" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H2" s="27" t="n">
         <v>200</v>
       </c>
       <c r="I2" s="28" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J2" s="29" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K2" s="27" t="n">
         <v>200</v>
       </c>
       <c r="L2" s="28" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M2" s="27" t="s">
         <v>26</v>
@@ -11460,40 +11729,40 @@
     </row>
     <row r="3" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="29" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B3" s="27" t="s">
         <v>109</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D3" s="28" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E3" s="29" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F3" s="28" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G3" s="30" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H3" s="27" t="n">
         <v>200</v>
       </c>
       <c r="I3" s="28" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J3" s="29" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K3" s="27" t="n">
         <v>200</v>
       </c>
       <c r="L3" s="28" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M3" s="27" t="s">
         <v>26</v>
@@ -11506,40 +11775,40 @@
     </row>
     <row r="4" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="29" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B4" s="27" t="s">
         <v>109</v>
       </c>
       <c r="C4" s="28" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D4" s="29" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E4" s="29" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F4" s="29" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G4" s="30" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H4" s="27" t="n">
         <v>200</v>
       </c>
       <c r="I4" s="28" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J4" s="29" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K4" s="27" t="n">
         <v>200</v>
       </c>
       <c r="L4" s="28" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M4" s="27" t="s">
         <v>26</v>
@@ -11552,40 +11821,40 @@
     </row>
     <row r="5" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="29" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B5" s="27" t="s">
         <v>109</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D5" s="29" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E5" s="29" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F5" s="29" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G5" s="30" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H5" s="27" t="n">
         <v>200</v>
       </c>
       <c r="I5" s="28" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J5" s="29" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K5" s="27" t="n">
         <v>200</v>
       </c>
       <c r="L5" s="28" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M5" s="27" t="s">
         <v>26</v>
@@ -11598,40 +11867,40 @@
     </row>
     <row r="6" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="29" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B6" s="27" t="s">
         <v>109</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F6" s="29" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G6" s="30" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H6" s="27" t="n">
         <v>200</v>
       </c>
       <c r="I6" s="28" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J6" s="29" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K6" s="27" t="n">
         <v>200</v>
       </c>
       <c r="L6" s="28" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M6" s="27" t="s">
         <v>26</v>
@@ -11644,40 +11913,40 @@
     </row>
     <row r="7" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="29" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B7" s="27" t="s">
         <v>109</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D7" s="29" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E7" s="29" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F7" s="28" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G7" s="30" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H7" s="27" t="n">
         <v>200</v>
       </c>
       <c r="I7" s="28" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J7" s="29" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K7" s="27" t="n">
         <v>200</v>
       </c>
       <c r="L7" s="28" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M7" s="27" t="s">
         <v>26</v>
@@ -11690,40 +11959,40 @@
     </row>
     <row r="8" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="29" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B8" s="27" t="s">
         <v>109</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E8" s="29" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F8" s="29" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G8" s="30" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H8" s="27" t="n">
         <v>200</v>
       </c>
       <c r="I8" s="28" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J8" s="29" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K8" s="27" t="n">
         <v>200</v>
       </c>
       <c r="L8" s="28" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M8" s="27" t="s">
         <v>26</v>
@@ -11736,40 +12005,40 @@
     </row>
     <row r="9" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="29" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B9" s="27" t="s">
         <v>109</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E9" s="29" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F9" s="29" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H9" s="27" t="n">
         <v>200</v>
       </c>
       <c r="I9" s="28" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J9" s="29" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K9" s="27" t="n">
         <v>200</v>
       </c>
       <c r="L9" s="28" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M9" s="27" t="s">
         <v>26</v>
@@ -11782,40 +12051,40 @@
     </row>
     <row r="10" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="29" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B10" s="27" t="s">
         <v>109</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D10" s="29" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E10" s="29" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F10" s="29" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="G10" s="30" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H10" s="27" t="n">
         <v>200</v>
       </c>
       <c r="I10" s="28" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J10" s="29" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K10" s="27" t="n">
         <v>200</v>
       </c>
       <c r="L10" s="28" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M10" s="27" t="s">
         <v>26</v>
@@ -11828,46 +12097,46 @@
     </row>
     <row r="11" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="29" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B11" s="27" t="s">
         <v>109</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D11" s="29" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E11" s="29" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F11" s="28" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G11" s="30" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H11" s="27" t="n">
         <v>400</v>
       </c>
       <c r="I11" s="28" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J11" s="28" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K11" s="27" t="n">
         <v>200</v>
       </c>
       <c r="L11" s="29" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M11" s="27" t="s">
         <v>27</v>
       </c>
       <c r="N11" s="27" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O11" s="28"/>
       <c r="P11" s="27" t="n">
@@ -11876,46 +12145,46 @@
     </row>
     <row r="12" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="29" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B12" s="27" t="s">
         <v>109</v>
       </c>
       <c r="C12" s="28" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D12" s="29" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E12" s="29" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F12" s="28" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G12" s="30" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H12" s="27" t="n">
         <v>400</v>
       </c>
       <c r="I12" s="28" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J12" s="28" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K12" s="27" t="n">
         <v>200</v>
       </c>
       <c r="L12" s="29" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M12" s="27" t="s">
         <v>27</v>
       </c>
       <c r="N12" s="27" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O12" s="28"/>
       <c r="P12" s="27" t="n">
@@ -11924,46 +12193,46 @@
     </row>
     <row r="13" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="29" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B13" s="27" t="s">
         <v>109</v>
       </c>
       <c r="C13" s="28" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D13" s="29" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E13" s="29" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F13" s="28" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G13" s="30" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H13" s="27" t="n">
         <v>400</v>
       </c>
       <c r="I13" s="28" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J13" s="28" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K13" s="27" t="n">
         <v>200</v>
       </c>
       <c r="L13" s="29" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M13" s="27" t="s">
         <v>27</v>
       </c>
       <c r="N13" s="27" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O13" s="28"/>
       <c r="P13" s="27" t="n">
@@ -11972,46 +12241,46 @@
     </row>
     <row r="14" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="29" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B14" s="27" t="s">
         <v>109</v>
       </c>
       <c r="C14" s="28" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D14" s="29" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E14" s="29" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F14" s="29" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G14" s="30" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H14" s="27" t="n">
         <v>400</v>
       </c>
       <c r="I14" s="28" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J14" s="28" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K14" s="27" t="n">
         <v>200</v>
       </c>
       <c r="L14" s="29" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M14" s="27" t="s">
         <v>27</v>
       </c>
       <c r="N14" s="27" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O14" s="28"/>
       <c r="P14" s="27" t="n">
@@ -12020,49 +12289,49 @@
     </row>
     <row r="15" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="29" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B15" s="27" t="s">
         <v>109</v>
       </c>
       <c r="C15" s="28" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D15" s="29" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E15" s="29" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F15" s="29" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G15" s="30" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H15" s="27" t="n">
         <v>400</v>
       </c>
       <c r="I15" s="28" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J15" s="28" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K15" s="27" t="n">
         <v>200</v>
       </c>
       <c r="L15" s="29" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M15" s="27" t="s">
         <v>27</v>
       </c>
       <c r="N15" s="27" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O15" s="28" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="P15" s="27" t="n">
         <v>14</v>
@@ -12070,49 +12339,49 @@
     </row>
     <row r="16" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="29" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B16" s="27" t="s">
         <v>109</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D16" s="29" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E16" s="29" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F16" s="29" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G16" s="30" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H16" s="27" t="n">
         <v>400</v>
       </c>
       <c r="I16" s="28" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J16" s="28" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K16" s="27" t="n">
         <v>200</v>
       </c>
       <c r="L16" s="29" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M16" s="27" t="s">
         <v>27</v>
       </c>
       <c r="N16" s="27" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O16" s="28" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P16" s="27" t="n">
         <v>15</v>
@@ -12120,49 +12389,49 @@
     </row>
     <row r="17" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="29" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B17" s="27" t="s">
         <v>109</v>
       </c>
       <c r="C17" s="28" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D17" s="29" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E17" s="29" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F17" s="29" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G17" s="30" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H17" s="27" t="n">
         <v>400</v>
       </c>
       <c r="I17" s="28" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J17" s="28" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K17" s="27" t="n">
         <v>200</v>
       </c>
       <c r="L17" s="29" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M17" s="27" t="s">
         <v>27</v>
       </c>
       <c r="N17" s="27" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O17" s="28" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P17" s="27" t="n">
         <v>16</v>
@@ -12170,46 +12439,46 @@
     </row>
     <row r="18" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="29" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B18" s="27" t="s">
         <v>109</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D18" s="29" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E18" s="29" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F18" s="28" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G18" s="30" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H18" s="27" t="n">
         <v>400</v>
       </c>
       <c r="I18" s="28" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J18" s="28" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K18" s="27" t="n">
         <v>200</v>
       </c>
       <c r="L18" s="29" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M18" s="27" t="s">
         <v>27</v>
       </c>
       <c r="N18" s="27" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O18" s="28"/>
       <c r="P18" s="27" t="n">
@@ -12218,46 +12487,46 @@
     </row>
     <row r="19" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="29" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B19" s="27" t="s">
         <v>109</v>
       </c>
       <c r="C19" s="28" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D19" s="29" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E19" s="29" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F19" s="28" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="G19" s="30" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H19" s="27" t="n">
         <v>400</v>
       </c>
       <c r="I19" s="28" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J19" s="28" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K19" s="27" t="n">
         <v>200</v>
       </c>
       <c r="L19" s="29" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M19" s="27" t="s">
         <v>27</v>
       </c>
       <c r="N19" s="27" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O19" s="28"/>
       <c r="P19" s="27" t="n">
@@ -12266,49 +12535,49 @@
     </row>
     <row r="20" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="29" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B20" s="27" t="s">
         <v>109</v>
       </c>
       <c r="C20" s="28" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D20" s="29" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E20" s="29" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F20" s="28" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G20" s="30" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H20" s="27" t="n">
         <v>400</v>
       </c>
       <c r="I20" s="28" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J20" s="28" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K20" s="27" t="n">
         <v>200</v>
       </c>
       <c r="L20" s="29" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M20" s="27" t="s">
         <v>27</v>
       </c>
       <c r="N20" s="27" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O20" s="29" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P20" s="27" t="n">
         <v>19</v>
@@ -12316,49 +12585,49 @@
     </row>
     <row r="21" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="29" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B21" s="27" t="s">
         <v>109</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D21" s="29" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E21" s="29" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F21" s="28" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G21" s="30" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H21" s="27" t="n">
         <v>400</v>
       </c>
       <c r="I21" s="28" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J21" s="28" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K21" s="27" t="n">
         <v>200</v>
       </c>
       <c r="L21" s="29" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M21" s="27" t="s">
         <v>27</v>
       </c>
       <c r="N21" s="27" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O21" s="29" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P21" s="27" t="n">
         <v>20</v>
@@ -12366,46 +12635,46 @@
     </row>
     <row r="22" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="29" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B22" s="27" t="s">
         <v>109</v>
       </c>
       <c r="C22" s="28" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D22" s="28" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E22" s="29" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F22" s="28" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G22" s="30" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H22" s="27" t="n">
         <v>400</v>
       </c>
       <c r="I22" s="28" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J22" s="28" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K22" s="27" t="n">
         <v>200</v>
       </c>
       <c r="L22" s="29" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M22" s="27" t="s">
         <v>27</v>
       </c>
       <c r="N22" s="27" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O22" s="28"/>
       <c r="P22" s="27" t="n">
@@ -12414,49 +12683,49 @@
     </row>
     <row r="23" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="29" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B23" s="27" t="s">
         <v>109</v>
       </c>
       <c r="C23" s="28" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D23" s="28" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E23" s="29" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F23" s="29" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G23" s="30" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H23" s="27" t="n">
         <v>400</v>
       </c>
       <c r="I23" s="28" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J23" s="28" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K23" s="27" t="n">
         <v>200</v>
       </c>
       <c r="L23" s="29" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M23" s="27" t="s">
         <v>27</v>
       </c>
       <c r="N23" s="27" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O23" s="28" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P23" s="27" t="n">
         <v>22</v>
@@ -12464,46 +12733,46 @@
     </row>
     <row r="24" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="29" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B24" s="27" t="s">
         <v>109</v>
       </c>
       <c r="C24" s="28" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D24" s="29" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E24" s="29" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F24" s="28" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="G24" s="30" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H24" s="27" t="n">
         <v>400</v>
       </c>
       <c r="I24" s="28" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J24" s="28" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K24" s="27" t="n">
         <v>200</v>
       </c>
       <c r="L24" s="29" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M24" s="27" t="s">
         <v>27</v>
       </c>
       <c r="N24" s="27" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O24" s="28"/>
       <c r="P24" s="27" t="n">
@@ -12512,46 +12781,46 @@
     </row>
     <row r="25" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="29" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B25" s="27" t="s">
         <v>109</v>
       </c>
       <c r="C25" s="28" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D25" s="29" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E25" s="29" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F25" s="29" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="G25" s="30" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H25" s="27" t="n">
         <v>400</v>
       </c>
       <c r="I25" s="28" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J25" s="28" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K25" s="27" t="n">
         <v>200</v>
       </c>
       <c r="L25" s="29" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="M25" s="27" t="s">
         <v>27</v>
       </c>
       <c r="N25" s="27" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O25" s="28"/>
       <c r="P25" s="27" t="n">
@@ -12560,46 +12829,46 @@
     </row>
     <row r="26" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="29" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B26" s="27" t="s">
         <v>109</v>
       </c>
       <c r="C26" s="28" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D26" s="29" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E26" s="29" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F26" s="28" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G26" s="30" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H26" s="27" t="n">
         <v>400</v>
       </c>
       <c r="I26" s="28" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J26" s="28" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K26" s="27" t="n">
         <v>200</v>
       </c>
       <c r="L26" s="29" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M26" s="27" t="s">
         <v>27</v>
       </c>
       <c r="N26" s="27" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O26" s="28"/>
       <c r="P26" s="27" t="n">
@@ -12608,49 +12877,49 @@
     </row>
     <row r="27" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="29" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B27" s="27" t="s">
         <v>109</v>
       </c>
       <c r="C27" s="28" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D27" s="29" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E27" s="29" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F27" s="28" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="G27" s="30" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H27" s="27" t="n">
         <v>400</v>
       </c>
       <c r="I27" s="28" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J27" s="28" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K27" s="27" t="n">
         <v>200</v>
       </c>
       <c r="L27" s="29" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M27" s="27" t="s">
         <v>27</v>
       </c>
       <c r="N27" s="27" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O27" s="28" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="P27" s="27" t="n">
         <v>26</v>
@@ -12658,46 +12927,46 @@
     </row>
     <row r="28" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="29" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B28" s="27" t="s">
         <v>109</v>
       </c>
       <c r="C28" s="28" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D28" s="29" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E28" s="29" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F28" s="28" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="G28" s="30" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H28" s="27" t="n">
         <v>400</v>
       </c>
       <c r="I28" s="28" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J28" s="28" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K28" s="27" t="n">
         <v>200</v>
       </c>
       <c r="L28" s="29" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M28" s="27" t="s">
         <v>27</v>
       </c>
       <c r="N28" s="27" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O28" s="28"/>
       <c r="P28" s="27" t="n">
@@ -12706,49 +12975,49 @@
     </row>
     <row r="29" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="29" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B29" s="27" t="s">
         <v>109</v>
       </c>
       <c r="C29" s="28" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D29" s="29" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E29" s="29" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F29" s="29" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G29" s="30" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H29" s="27" t="n">
         <v>200</v>
       </c>
       <c r="I29" s="28" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J29" s="29" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K29" s="27" t="n">
         <v>200</v>
       </c>
       <c r="L29" s="29" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M29" s="27" t="s">
         <v>27</v>
       </c>
       <c r="N29" s="27" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O29" s="28" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="P29" s="27" t="n">
         <v>28</v>
@@ -12756,46 +13025,46 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="29" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B30" s="27" t="s">
         <v>109</v>
       </c>
       <c r="C30" s="28" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D30" s="28" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E30" s="29" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F30" s="28" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="G30" s="30" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H30" s="27" t="n">
         <v>400</v>
       </c>
       <c r="I30" s="28" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J30" s="28" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K30" s="27" t="n">
         <v>200</v>
       </c>
       <c r="L30" s="28" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M30" s="27" t="s">
         <v>27</v>
       </c>
       <c r="N30" s="27" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O30" s="28"/>
       <c r="P30" s="27" t="n">
@@ -12804,46 +13073,46 @@
     </row>
     <row r="31" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="29" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B31" s="27" t="s">
         <v>109</v>
       </c>
       <c r="C31" s="28" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D31" s="29" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E31" s="29" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F31" s="29" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="G31" s="30" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H31" s="27" t="n">
         <v>400</v>
       </c>
       <c r="I31" s="28" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J31" s="28" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K31" s="27" t="n">
         <v>200</v>
       </c>
       <c r="L31" s="29" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M31" s="27" t="s">
         <v>27</v>
       </c>
       <c r="N31" s="27" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O31" s="28"/>
       <c r="P31" s="27" t="n">
@@ -12852,49 +13121,49 @@
     </row>
     <row r="32" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="29" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B32" s="27" t="s">
         <v>109</v>
       </c>
       <c r="C32" s="28" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D32" s="29" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E32" s="29" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F32" s="29" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="G32" s="30" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H32" s="27" t="n">
         <v>400</v>
       </c>
       <c r="I32" s="28" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J32" s="28" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K32" s="27" t="n">
         <v>200</v>
       </c>
       <c r="L32" s="29" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M32" s="27" t="s">
         <v>27</v>
       </c>
       <c r="N32" s="27" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O32" s="28" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="P32" s="27" t="n">
         <v>31</v>
@@ -12902,46 +13171,46 @@
     </row>
     <row r="33" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="29" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B33" s="27" t="s">
         <v>109</v>
       </c>
       <c r="C33" s="28" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D33" s="28" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E33" s="29" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F33" s="28" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G33" s="30" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H33" s="27" t="n">
         <v>400</v>
       </c>
       <c r="I33" s="28" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J33" s="28" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K33" s="27" t="n">
         <v>200</v>
       </c>
       <c r="L33" s="28" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M33" s="27" t="s">
         <v>27</v>
       </c>
       <c r="N33" s="27" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O33" s="28"/>
       <c r="P33" s="27" t="n">
@@ -12950,46 +13219,46 @@
     </row>
     <row r="34" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="29" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B34" s="27" t="s">
         <v>109</v>
       </c>
       <c r="C34" s="28" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D34" s="28" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E34" s="29" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F34" s="28" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="G34" s="30" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H34" s="27" t="n">
         <v>400</v>
       </c>
       <c r="I34" s="28" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J34" s="28" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K34" s="27" t="n">
         <v>200</v>
       </c>
       <c r="L34" s="28" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M34" s="27" t="s">
         <v>27</v>
       </c>
       <c r="N34" s="27" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O34" s="28"/>
       <c r="P34" s="27" t="n">
@@ -13041,442 +13310,442 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="22" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B1" s="31" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C1" s="22" t="s">
         <v>3</v>
       </c>
       <c r="D1" s="22" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E1" s="22" t="s">
         <v>38</v>
       </c>
       <c r="F1" s="22" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="27" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C2" s="28" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D2" s="29" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E2" s="33" t="s">
         <v>42</v>
       </c>
       <c r="F2" s="27" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B3" s="29" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E3" s="33" t="s">
         <v>43</v>
       </c>
       <c r="F3" s="27" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="27" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C4" s="28" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D4" s="29" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E4" s="33" t="s">
         <v>42</v>
       </c>
       <c r="F4" s="27" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D5" s="29" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E5" s="33" t="s">
         <v>42</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="27" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E6" s="33" t="s">
         <v>42</v>
       </c>
       <c r="F6" s="27" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C7" s="29" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D7" s="29" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E7" s="33" t="s">
         <v>43</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="27" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B8" s="29" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E8" s="33" t="s">
         <v>42</v>
       </c>
       <c r="F8" s="27" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B9" s="29" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E9" s="33" t="s">
         <v>42</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="27" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B10" s="29" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D10" s="29" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E10" s="33" t="s">
         <v>42</v>
       </c>
       <c r="F10" s="27" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D11" s="29" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E11" s="33" t="s">
         <v>42</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="27" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D12" s="29" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E12" s="33" t="s">
         <v>43</v>
       </c>
       <c r="F12" s="27" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B13" s="29" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C13" s="28" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D13" s="29" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E13" s="33" t="s">
         <v>42</v>
       </c>
       <c r="F13" s="27" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="27" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B14" s="29" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C14" s="28" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D14" s="29" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E14" s="33" t="s">
         <v>42</v>
       </c>
       <c r="F14" s="27" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B15" s="29" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C15" s="29" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D15" s="29" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E15" s="33" t="s">
         <v>43</v>
       </c>
       <c r="F15" s="27" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="27" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B16" s="29" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D16" s="29" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E16" s="33" t="s">
         <v>42</v>
       </c>
       <c r="F16" s="27" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B17" s="29" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C17" s="28" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D17" s="29" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E17" s="33" t="s">
         <v>42</v>
       </c>
       <c r="F17" s="27" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="27" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B18" s="29" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D18" s="29" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E18" s="33" t="s">
         <v>43</v>
       </c>
       <c r="F18" s="27" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B19" s="29" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C19" s="29" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D19" s="29" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E19" s="33" t="s">
         <v>42</v>
       </c>
       <c r="F19" s="27" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="27" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B20" s="29" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D20" s="29" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E20" s="33" t="s">
         <v>45</v>
       </c>
       <c r="F20" s="27" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="27" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B21" s="29" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C21" s="29" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D21" s="29" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E21" s="33" t="s">
         <v>45</v>
       </c>
       <c r="F21" s="27" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="27" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B22" s="29" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C22" s="28" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D22" s="29" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E22" s="33" t="s">
         <v>44</v>
       </c>
       <c r="F22" s="27" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
   </sheetData>
